--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/158.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/158.xlsx
@@ -426,13 +426,13 @@
         <v>-0.8912335570791303</v>
       </c>
       <c r="E2">
-        <v>-13.59554523912582</v>
+        <v>-13.58712227747155</v>
       </c>
       <c r="F2">
-        <v>0.01188443988045675</v>
+        <v>-0.4652667812756976</v>
       </c>
       <c r="G2">
-        <v>-8.45020836620451</v>
+        <v>-6.865244962731958</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.547988296273447</v>
       </c>
       <c r="E3">
-        <v>-13.38826792684673</v>
+        <v>-14.11216713934287</v>
       </c>
       <c r="F3">
-        <v>-0.1001257435912868</v>
+        <v>-0.5165344398349591</v>
       </c>
       <c r="G3">
-        <v>-7.992988921775766</v>
+        <v>-7.106702912184241</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.315953371837626</v>
       </c>
       <c r="E4">
-        <v>-14.13564727707265</v>
+        <v>-14.67608442209604</v>
       </c>
       <c r="F4">
-        <v>-0.1897153349388589</v>
+        <v>-0.3229540898421454</v>
       </c>
       <c r="G4">
-        <v>-8.474630260647714</v>
+        <v>-7.247718909975037</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.092087294352946</v>
       </c>
       <c r="E5">
-        <v>-15.0966483316624</v>
+        <v>-15.06906539648167</v>
       </c>
       <c r="F5">
-        <v>-0.2825819477319059</v>
+        <v>-0.2433951993750725</v>
       </c>
       <c r="G5">
-        <v>-8.519931765807101</v>
+        <v>-7.013021094513945</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.849302145420854</v>
       </c>
       <c r="E6">
-        <v>-15.19226253186035</v>
+        <v>-16.10482702846405</v>
       </c>
       <c r="F6">
-        <v>-0.5074588465698877</v>
+        <v>-0.2219388269077597</v>
       </c>
       <c r="G6">
-        <v>-7.638810207256839</v>
+        <v>-7.168941168322539</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.528562617040018</v>
       </c>
       <c r="E7">
-        <v>-15.58640732406595</v>
+        <v>-15.88427675886849</v>
       </c>
       <c r="F7">
-        <v>-0.3265409206962673</v>
+        <v>-0.01632809712408881</v>
       </c>
       <c r="G7">
-        <v>-7.553295505431924</v>
+        <v>-7.123937612261687</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.094361411722182</v>
       </c>
       <c r="E8">
-        <v>-17.19138002491647</v>
+        <v>-17.3787909217239</v>
       </c>
       <c r="F8">
-        <v>0.04256551174534484</v>
+        <v>0.120045200031391</v>
       </c>
       <c r="G8">
-        <v>-7.468257522164666</v>
+        <v>-6.283393410386272</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.50317818880802</v>
       </c>
       <c r="E9">
-        <v>-17.58413004712771</v>
+        <v>-18.34523067359686</v>
       </c>
       <c r="F9">
-        <v>-0.134913032671852</v>
+        <v>0.0791735523772634</v>
       </c>
       <c r="G9">
-        <v>-6.629318934875797</v>
+        <v>-6.600318555951781</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.724978513345476</v>
       </c>
       <c r="E10">
-        <v>-17.49237410678429</v>
+        <v>-18.92850718273282</v>
       </c>
       <c r="F10">
-        <v>-0.06440736954997492</v>
+        <v>-0.2708796014325573</v>
       </c>
       <c r="G10">
-        <v>-6.282804133280282</v>
+        <v>-5.341844464107693</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.734062352783154</v>
       </c>
       <c r="E11">
-        <v>-18.24909569888803</v>
+        <v>-19.79933273440783</v>
       </c>
       <c r="F11">
-        <v>0.04419242532444307</v>
+        <v>0.2448453762023589</v>
       </c>
       <c r="G11">
-        <v>-6.75898638255797</v>
+        <v>-5.497218297902307</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.521231943559591</v>
       </c>
       <c r="E12">
-        <v>-18.95973101101571</v>
+        <v>-20.92589479871801</v>
       </c>
       <c r="F12">
-        <v>0.1387455941495898</v>
+        <v>0.1623681473752233</v>
       </c>
       <c r="G12">
-        <v>-6.269297107480055</v>
+        <v>-5.040932427315639</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.083802593202298</v>
       </c>
       <c r="E13">
-        <v>-20.33834793859282</v>
+        <v>-21.2271062473382</v>
       </c>
       <c r="F13">
-        <v>0.2820307889140287</v>
+        <v>0.1660916588508071</v>
       </c>
       <c r="G13">
-        <v>-4.567312540285346</v>
+        <v>-4.366680238423355</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.43473728214569</v>
       </c>
       <c r="E14">
-        <v>-20.93650048484397</v>
+        <v>-21.78949290587678</v>
       </c>
       <c r="F14">
-        <v>0.238011345129263</v>
+        <v>0.3208364882655744</v>
       </c>
       <c r="G14">
-        <v>-5.060348776903464</v>
+        <v>-3.901207603965207</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.601759152349789</v>
       </c>
       <c r="E15">
-        <v>-22.52665601874139</v>
+        <v>-22.45639221603837</v>
       </c>
       <c r="F15">
-        <v>0.02215536730776782</v>
+        <v>0.05641001614833298</v>
       </c>
       <c r="G15">
-        <v>-3.390877077449936</v>
+        <v>-1.958281532422341</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.614794537965238</v>
       </c>
       <c r="E16">
-        <v>-23.35523543639884</v>
+        <v>-23.61035607656897</v>
       </c>
       <c r="F16">
-        <v>0.9466042767905853</v>
+        <v>1.05593386334687</v>
       </c>
       <c r="G16">
-        <v>-5.06072617909494</v>
+        <v>-2.54070911969186</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.517603940447899</v>
       </c>
       <c r="E17">
-        <v>-23.48678760632167</v>
+        <v>-24.09358953792747</v>
       </c>
       <c r="F17">
-        <v>0.4342010524408951</v>
+        <v>0.5062375385231457</v>
       </c>
       <c r="G17">
-        <v>-2.821939963252947</v>
+        <v>-2.115850257909492</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.355544353851997</v>
       </c>
       <c r="E18">
-        <v>-25.26582126260501</v>
+        <v>-26.92512659459955</v>
       </c>
       <c r="F18">
-        <v>0.6094065567048101</v>
+        <v>0.6292948296786235</v>
       </c>
       <c r="G18">
-        <v>-2.677778947199844</v>
+        <v>-2.274266483054697</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.8266857010728552</v>
       </c>
       <c r="E19">
-        <v>-25.54650061007442</v>
+        <v>-25.8392619261963</v>
       </c>
       <c r="F19">
-        <v>0.7239457458573005</v>
+        <v>0.7022342362299255</v>
       </c>
       <c r="G19">
-        <v>-2.690597379527902</v>
+        <v>-1.013316103147234</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.978957153863752</v>
       </c>
       <c r="E20">
-        <v>-25.65691386332944</v>
+        <v>-27.3635779764962</v>
       </c>
       <c r="F20">
-        <v>1.141679829945452</v>
+        <v>1.387507797135039</v>
       </c>
       <c r="G20">
-        <v>-1.703508568811109</v>
+        <v>-0.633113190144095</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.062390716333108</v>
       </c>
       <c r="E21">
-        <v>-26.73558278653449</v>
+        <v>-27.98901005016956</v>
       </c>
       <c r="F21">
-        <v>1.532047968514719</v>
+        <v>1.36821843379345</v>
       </c>
       <c r="G21">
-        <v>-2.183180133087189</v>
+        <v>-1.343840969788069</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.036721357816635</v>
       </c>
       <c r="E22">
-        <v>-26.59830662546598</v>
+        <v>-28.72717848426387</v>
       </c>
       <c r="F22">
-        <v>1.139726539609651</v>
+        <v>0.9465761122988902</v>
       </c>
       <c r="G22">
-        <v>-0.821549442239411</v>
+        <v>-0.6450708806319425</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.866615059784729</v>
       </c>
       <c r="E23">
-        <v>-27.86900548896629</v>
+        <v>-29.18095875067649</v>
       </c>
       <c r="F23">
-        <v>1.24096463337539</v>
+        <v>1.389987929139021</v>
       </c>
       <c r="G23">
-        <v>-1.364025365941006</v>
+        <v>0.01889213272428675</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>5.53274159282818</v>
       </c>
       <c r="E24">
-        <v>-29.09525738008132</v>
+        <v>-28.62642446606721</v>
       </c>
       <c r="F24">
-        <v>2.037101917266772</v>
+        <v>1.764237694784615</v>
       </c>
       <c r="G24">
-        <v>-1.218983744774456</v>
+        <v>-0.9188728600029054</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>6.015222527985688</v>
       </c>
       <c r="E25">
-        <v>-29.37510801680734</v>
+        <v>-29.91754674734213</v>
       </c>
       <c r="F25">
-        <v>1.452571086420523</v>
+        <v>1.864004608042982</v>
       </c>
       <c r="G25">
-        <v>-0.8147230973374338</v>
+        <v>0.10182129848303</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.307429142720061</v>
       </c>
       <c r="E26">
-        <v>-29.34155655288451</v>
+        <v>-30.13734302601542</v>
       </c>
       <c r="F26">
-        <v>1.356013268480602</v>
+        <v>1.859650708973868</v>
       </c>
       <c r="G26">
-        <v>-0.4143258565447408</v>
+        <v>0.4101588889196698</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.411864468942421</v>
       </c>
       <c r="E27">
-        <v>-28.90733476571102</v>
+        <v>-31.47846418880902</v>
       </c>
       <c r="F27">
-        <v>1.757383782893852</v>
+        <v>2.020435165122446</v>
       </c>
       <c r="G27">
-        <v>-1.113188640975967</v>
+        <v>-0.009727533462712662</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.335940012563962</v>
       </c>
       <c r="E28">
-        <v>-30.01019479706505</v>
+        <v>-30.8488070488865</v>
       </c>
       <c r="F28">
-        <v>1.826830792474951</v>
+        <v>1.260308668965564</v>
       </c>
       <c r="G28">
-        <v>-1.651450240206069</v>
+        <v>0.04224472095830571</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.094737895552277</v>
       </c>
       <c r="E29">
-        <v>-27.35180394407626</v>
+        <v>-30.63130217806109</v>
       </c>
       <c r="F29">
-        <v>1.534183499679136</v>
+        <v>1.717637058172726</v>
       </c>
       <c r="G29">
-        <v>-0.8637191713186474</v>
+        <v>-0.2526487440433538</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.705909075101133</v>
       </c>
       <c r="E30">
-        <v>-29.35553142367218</v>
+        <v>-29.84334090801543</v>
       </c>
       <c r="F30">
-        <v>1.636420604532651</v>
+        <v>1.500046479009769</v>
       </c>
       <c r="G30">
-        <v>-1.804086252839707</v>
+        <v>-0.5489856069001355</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.19078885414718</v>
       </c>
       <c r="E31">
-        <v>-28.63033706760984</v>
+        <v>-29.50604431426512</v>
       </c>
       <c r="F31">
-        <v>1.755685629718113</v>
+        <v>1.5380784832071</v>
       </c>
       <c r="G31">
-        <v>-1.688975273893708</v>
+        <v>-0.6157195838807642</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.567894557112997</v>
       </c>
       <c r="E32">
-        <v>-29.82375525793226</v>
+        <v>-29.73532095327347</v>
       </c>
       <c r="F32">
-        <v>1.719411421149522</v>
+        <v>1.436492475132185</v>
       </c>
       <c r="G32">
-        <v>-0.8437963082633133</v>
+        <v>-0.9693123318392411</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.859950876664046</v>
       </c>
       <c r="E33">
-        <v>-28.35765500523797</v>
+        <v>-30.13117298017997</v>
       </c>
       <c r="F33">
-        <v>2.057015869630072</v>
+        <v>1.406725920879987</v>
       </c>
       <c r="G33">
-        <v>-0.6984567379982297</v>
+        <v>-0.8113231670686023</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.090505955394065</v>
       </c>
       <c r="E34">
-        <v>-28.49651613220917</v>
+        <v>-29.66070075857508</v>
       </c>
       <c r="F34">
-        <v>1.530906478233661</v>
+        <v>1.288729954555615</v>
       </c>
       <c r="G34">
-        <v>-2.491554139524761</v>
+        <v>-1.410419351128352</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.276945522432108</v>
       </c>
       <c r="E35">
-        <v>-27.29780189153479</v>
+        <v>-27.64211988423399</v>
       </c>
       <c r="F35">
-        <v>2.425718887146521</v>
+        <v>1.865614954274024</v>
       </c>
       <c r="G35">
-        <v>-3.172738610776279</v>
+        <v>-1.179717364133161</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.4443747531061</v>
       </c>
       <c r="E36">
-        <v>-26.80407595590051</v>
+        <v>-28.40636327166447</v>
       </c>
       <c r="F36">
-        <v>1.876973528101211</v>
+        <v>1.865727612240805</v>
       </c>
       <c r="G36">
-        <v>-1.971434329849865</v>
+        <v>-2.174983222331954</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.6121232867482306</v>
       </c>
       <c r="E37">
-        <v>-27.30706714935448</v>
+        <v>-28.1405871321543</v>
       </c>
       <c r="F37">
-        <v>2.329822106394033</v>
+        <v>1.958456716044987</v>
       </c>
       <c r="G37">
-        <v>-2.730052461264936</v>
+        <v>-1.386252368691672</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2032099689167201</v>
       </c>
       <c r="E38">
-        <v>-27.03822523294111</v>
+        <v>-28.48315713388655</v>
       </c>
       <c r="F38">
-        <v>1.821138251682913</v>
+        <v>2.09737558622927</v>
       </c>
       <c r="G38">
-        <v>-2.040687631985879</v>
+        <v>-1.468175128606477</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.9811878361412308</v>
       </c>
       <c r="E39">
-        <v>-25.66673159497807</v>
+        <v>-27.98707639176828</v>
       </c>
       <c r="F39">
-        <v>2.331730664890083</v>
+        <v>2.087234712484198</v>
       </c>
       <c r="G39">
-        <v>-2.515429793953985</v>
+        <v>-1.856823243280297</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.709879272262228</v>
       </c>
       <c r="E40">
-        <v>-25.08021722692663</v>
+        <v>-26.74842101034624</v>
       </c>
       <c r="F40">
-        <v>2.383687525128474</v>
+        <v>1.955900374239948</v>
       </c>
       <c r="G40">
-        <v>-2.302965602334639</v>
+        <v>-2.276852019120868</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.375294091951476</v>
       </c>
       <c r="E41">
-        <v>-22.36682805711467</v>
+        <v>-25.06425435604959</v>
       </c>
       <c r="F41">
-        <v>2.04434184836724</v>
+        <v>2.06440987706746</v>
       </c>
       <c r="G41">
-        <v>-4.063460751390428</v>
+        <v>-2.707401708685243</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.963889255295691</v>
       </c>
       <c r="E42">
-        <v>-23.94053617341623</v>
+        <v>-24.52194695126103</v>
       </c>
       <c r="F42">
-        <v>2.114835914345478</v>
+        <v>2.029706253094578</v>
       </c>
       <c r="G42">
-        <v>-3.371513696590739</v>
+        <v>-2.324523874886373</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.473589046875526</v>
       </c>
       <c r="E43">
-        <v>-21.88417424042915</v>
+        <v>-25.193791355039</v>
       </c>
       <c r="F43">
-        <v>1.802846242694294</v>
+        <v>2.260360186199684</v>
       </c>
       <c r="G43">
-        <v>-3.014289280175682</v>
+        <v>-2.590863884611818</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.897933965781375</v>
       </c>
       <c r="E44">
-        <v>-22.91373639149503</v>
+        <v>-23.64912887102264</v>
       </c>
       <c r="F44">
-        <v>2.652168027315016</v>
+        <v>2.245005568021392</v>
       </c>
       <c r="G44">
-        <v>-3.157493548567936</v>
+        <v>-2.924507285150647</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.234301064015514</v>
       </c>
       <c r="E45">
-        <v>-22.1436195732766</v>
+        <v>-23.11844605901177</v>
       </c>
       <c r="F45">
-        <v>2.364030366660042</v>
+        <v>2.330900640752478</v>
       </c>
       <c r="G45">
-        <v>-2.635605907575068</v>
+        <v>-2.285631585891015</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.489029064407449</v>
       </c>
       <c r="E46">
-        <v>-21.6304574272014</v>
+        <v>-22.34931644812701</v>
       </c>
       <c r="F46">
-        <v>2.529852953352447</v>
+        <v>2.375445269470619</v>
       </c>
       <c r="G46">
-        <v>-2.825899375717916</v>
+        <v>-1.880377774792211</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.667019650291236</v>
       </c>
       <c r="E47">
-        <v>-20.05138306920076</v>
+        <v>-22.15553398839078</v>
       </c>
       <c r="F47">
-        <v>2.202999057025429</v>
+        <v>2.323042747569522</v>
       </c>
       <c r="G47">
-        <v>-3.726351209671982</v>
+        <v>-3.323077104805662</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.776744552298864</v>
       </c>
       <c r="E48">
-        <v>-18.95095482838884</v>
+        <v>-22.34699334096107</v>
       </c>
       <c r="F48">
-        <v>2.950294142112947</v>
+        <v>2.061520531566496</v>
       </c>
       <c r="G48">
-        <v>-3.578879648079608</v>
+        <v>-2.344896972135048</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.833688176371872</v>
       </c>
       <c r="E49">
-        <v>-19.3546320583806</v>
+        <v>-20.68495733913991</v>
       </c>
       <c r="F49">
-        <v>2.375745138470432</v>
+        <v>2.347754603929837</v>
       </c>
       <c r="G49">
-        <v>-4.231762265515896</v>
+        <v>-2.462282295866526</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.850176501688454</v>
       </c>
       <c r="E50">
-        <v>-16.45242816481882</v>
+        <v>-19.65677184417236</v>
       </c>
       <c r="F50">
-        <v>2.926153859260564</v>
+        <v>2.357501174791176</v>
       </c>
       <c r="G50">
-        <v>-2.946982578816759</v>
+        <v>-3.462245818185544</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.840920534681857</v>
       </c>
       <c r="E51">
-        <v>-19.26603699289453</v>
+        <v>-19.95166607155186</v>
       </c>
       <c r="F51">
-        <v>2.605746318062132</v>
+        <v>2.619540292053549</v>
       </c>
       <c r="G51">
-        <v>-4.143552779622016</v>
+        <v>-3.365117722608867</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.825930703383051</v>
       </c>
       <c r="E52">
-        <v>-17.0693648212538</v>
+        <v>-19.59739902145779</v>
       </c>
       <c r="F52">
-        <v>2.99329469399227</v>
+        <v>2.277876843299282</v>
       </c>
       <c r="G52">
-        <v>-3.252284398993887</v>
+        <v>-2.954235984093303</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.815612767058174</v>
       </c>
       <c r="E53">
-        <v>-15.60702546622288</v>
+        <v>-17.3175659531402</v>
       </c>
       <c r="F53">
-        <v>2.695962155166221</v>
+        <v>2.354429588461596</v>
       </c>
       <c r="G53">
-        <v>-4.840710633100517</v>
+        <v>-2.800027462328511</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.826311009741454</v>
       </c>
       <c r="E54">
-        <v>-16.16535461205058</v>
+        <v>-17.87110850194179</v>
       </c>
       <c r="F54">
-        <v>2.396939746838461</v>
+        <v>2.415858001583596</v>
       </c>
       <c r="G54">
-        <v>-4.994306703940543</v>
+        <v>-3.398358910368689</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.874434174339425</v>
       </c>
       <c r="E55">
-        <v>-14.76118803412219</v>
+        <v>-17.55398852413265</v>
       </c>
       <c r="F55">
-        <v>2.526508005779943</v>
+        <v>2.560905133813789</v>
       </c>
       <c r="G55">
-        <v>-3.965965185258892</v>
+        <v>-4.482357320656568</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.963032213425031</v>
       </c>
       <c r="E56">
-        <v>-15.09917974863268</v>
+        <v>-16.41808421794465</v>
       </c>
       <c r="F56">
-        <v>2.687670197464197</v>
+        <v>2.088631339925318</v>
       </c>
       <c r="G56">
-        <v>-5.073607511788245</v>
+        <v>-4.0909316582753</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.102195068909047</v>
       </c>
       <c r="E57">
-        <v>-16.25330663422755</v>
+        <v>-15.26322371956054</v>
       </c>
       <c r="F57">
-        <v>2.493530699474494</v>
+        <v>2.501970106574215</v>
       </c>
       <c r="G57">
-        <v>-4.453085476998332</v>
+        <v>-4.818675641991128</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.293331089346774</v>
       </c>
       <c r="E58">
-        <v>-14.29706020460205</v>
+        <v>-16.06565572829771</v>
       </c>
       <c r="F58">
-        <v>2.533585576869462</v>
+        <v>2.437128819752681</v>
       </c>
       <c r="G58">
-        <v>-5.077818525714198</v>
+        <v>-5.162098394052964</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.527958983190585</v>
       </c>
       <c r="E59">
-        <v>-14.23028332688494</v>
+        <v>-13.77648041810229</v>
       </c>
       <c r="F59">
-        <v>2.83196848556226</v>
+        <v>2.273050774810572</v>
       </c>
       <c r="G59">
-        <v>-6.465211881948585</v>
+        <v>-5.541804725225212</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.803845409122977</v>
       </c>
       <c r="E60">
-        <v>-13.32962871692141</v>
+        <v>-13.85226895909466</v>
       </c>
       <c r="F60">
-        <v>2.80106209776381</v>
+        <v>2.501797806154433</v>
       </c>
       <c r="G60">
-        <v>-6.085280433679666</v>
+        <v>-4.922871752294149</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.104831965697154</v>
       </c>
       <c r="E61">
-        <v>-13.8174042377096</v>
+        <v>-13.99570837328762</v>
       </c>
       <c r="F61">
-        <v>2.210938130213859</v>
+        <v>2.544211873912573</v>
       </c>
       <c r="G61">
-        <v>-5.597676802291492</v>
+        <v>-5.727827589622399</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.413058606336458</v>
       </c>
       <c r="E62">
-        <v>-11.95757807665542</v>
+        <v>-13.31775052959929</v>
       </c>
       <c r="F62">
-        <v>2.239496924792775</v>
+        <v>2.211615734749349</v>
       </c>
       <c r="G62">
-        <v>-6.104491529444057</v>
+        <v>-5.257190504122989</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.716605434986292</v>
       </c>
       <c r="E63">
-        <v>-12.45744009457009</v>
+        <v>-12.69207844680352</v>
       </c>
       <c r="F63">
-        <v>2.307911788589986</v>
+        <v>2.306974076690017</v>
       </c>
       <c r="G63">
-        <v>-5.538656396417365</v>
+        <v>-6.056412476577222</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.9903500888187</v>
       </c>
       <c r="E64">
-        <v>-11.93667011216201</v>
+        <v>-12.04681618545057</v>
       </c>
       <c r="F64">
-        <v>2.805076366197777</v>
+        <v>1.988228240501601</v>
       </c>
       <c r="G64">
-        <v>-6.02048974693059</v>
+        <v>-6.149637438963098</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.216495160601185</v>
       </c>
       <c r="E65">
-        <v>-11.95221183495633</v>
+        <v>-12.89204227356022</v>
       </c>
       <c r="F65">
-        <v>2.730798317923551</v>
+        <v>2.576723637737648</v>
       </c>
       <c r="G65">
-        <v>-5.992363352028942</v>
+        <v>-6.127470026032138</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.378500004215566</v>
       </c>
       <c r="E66">
-        <v>-12.15819400366922</v>
+        <v>-13.09651646042856</v>
       </c>
       <c r="F66">
-        <v>2.083011695464726</v>
+        <v>1.802359162661448</v>
       </c>
       <c r="G66">
-        <v>-6.092871514601216</v>
+        <v>-6.05328732158815</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.453640659670615</v>
       </c>
       <c r="E67">
-        <v>-10.05691866547407</v>
+        <v>-12.17260360796163</v>
       </c>
       <c r="F67">
-        <v>2.414670122727981</v>
+        <v>1.760062723074505</v>
       </c>
       <c r="G67">
-        <v>-6.263490410604174</v>
+        <v>-5.98823841228701</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.429679275335183</v>
       </c>
       <c r="E68">
-        <v>-12.33299762883931</v>
+        <v>-11.60264081240822</v>
       </c>
       <c r="F68">
-        <v>2.530300271749959</v>
+        <v>1.789299122188911</v>
       </c>
       <c r="G68">
-        <v>-6.486872781412036</v>
+        <v>-5.885743922391174</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.297549453689029</v>
       </c>
       <c r="E69">
-        <v>-11.78108985915448</v>
+        <v>-12.18387045129271</v>
       </c>
       <c r="F69">
-        <v>2.189596072448133</v>
+        <v>1.823114736305993</v>
       </c>
       <c r="G69">
-        <v>-6.278212406617313</v>
+        <v>-5.937461264805669</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.049029389723388</v>
       </c>
       <c r="E70">
-        <v>-11.54259324706651</v>
+        <v>-11.32293961532446</v>
       </c>
       <c r="F70">
-        <v>2.238658616981142</v>
+        <v>1.563441436346015</v>
       </c>
       <c r="G70">
-        <v>-6.941867539238389</v>
+        <v>-7.025624341381951</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.688356228146474</v>
       </c>
       <c r="E71">
-        <v>-11.38240753599319</v>
+        <v>-11.29096858883031</v>
       </c>
       <c r="F71">
-        <v>1.54160567160822</v>
+        <v>1.606710379263844</v>
       </c>
       <c r="G71">
-        <v>-6.929032554182635</v>
+        <v>-6.009594741560848</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.222349086936867</v>
       </c>
       <c r="E72">
-        <v>-11.27138746722114</v>
+        <v>-11.89846337695929</v>
       </c>
       <c r="F72">
-        <v>2.197207112145055</v>
+        <v>1.224369120827704</v>
       </c>
       <c r="G72">
-        <v>-6.26877735183039</v>
+        <v>-6.676050595708149</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.658177625727347</v>
       </c>
       <c r="E73">
-        <v>-11.70200006061052</v>
+        <v>-12.33136284972254</v>
       </c>
       <c r="F73">
-        <v>1.780044601564835</v>
+        <v>1.105917552431792</v>
       </c>
       <c r="G73">
-        <v>-5.588943583158894</v>
+        <v>-6.170454149314035</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.016078952026127</v>
       </c>
       <c r="E74">
-        <v>-11.65220496042217</v>
+        <v>-12.40807519941247</v>
       </c>
       <c r="F74">
-        <v>1.358765104992702</v>
+        <v>0.977696218887262</v>
       </c>
       <c r="G74">
-        <v>-6.643779397791334</v>
+        <v>-6.165925323016313</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.313340187252907</v>
       </c>
       <c r="E75">
-        <v>-12.07636447835062</v>
+        <v>-12.52365544151024</v>
       </c>
       <c r="F75">
-        <v>1.377380177268412</v>
+        <v>1.260722852666963</v>
       </c>
       <c r="G75">
-        <v>-5.698919905973483</v>
+        <v>-6.354907815125609</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.567308618374505</v>
       </c>
       <c r="E76">
-        <v>-11.31674919135598</v>
+        <v>-12.05880758462288</v>
       </c>
       <c r="F76">
-        <v>1.62911440403996</v>
+        <v>1.194075724907326</v>
       </c>
       <c r="G76">
-        <v>-6.005963073104268</v>
+        <v>-6.187539874842214</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.803241164960338</v>
       </c>
       <c r="E77">
-        <v>-13.77258140198168</v>
+        <v>-13.38046536613151</v>
       </c>
       <c r="F77">
-        <v>0.7591728980287523</v>
+        <v>0.8605882624186902</v>
       </c>
       <c r="G77">
-        <v>-5.255482262624725</v>
+        <v>-5.744211479496252</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.038543238203165</v>
       </c>
       <c r="E78">
-        <v>-13.06155664108934</v>
+        <v>-13.51682677545048</v>
       </c>
       <c r="F78">
-        <v>1.049943110289824</v>
+        <v>0.9943530306227544</v>
       </c>
       <c r="G78">
-        <v>-5.291646662095724</v>
+        <v>-5.741208814692134</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.291886905216537</v>
       </c>
       <c r="E79">
-        <v>-14.00936625089475</v>
+        <v>-13.34407907747988</v>
       </c>
       <c r="F79">
-        <v>0.7736792679865773</v>
+        <v>0.5868907023293167</v>
       </c>
       <c r="G79">
-        <v>-4.953914737815896</v>
+        <v>-4.898320746574914</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.582127140477677</v>
       </c>
       <c r="E80">
-        <v>-14.52777689834484</v>
+        <v>-14.41676588652081</v>
       </c>
       <c r="F80">
-        <v>0.6806726611024572</v>
+        <v>0.7070346253291486</v>
       </c>
       <c r="G80">
-        <v>-4.464923987846766</v>
+        <v>-5.111268277842994</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.08285130618596621</v>
       </c>
       <c r="E81">
-        <v>-15.39267920601781</v>
+        <v>-14.99779174407495</v>
       </c>
       <c r="F81">
-        <v>0.5645786263349121</v>
+        <v>0.6291830000792455</v>
       </c>
       <c r="G81">
-        <v>-4.868145123984458</v>
+        <v>-4.483678228326737</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.6913104931989984</v>
       </c>
       <c r="E82">
-        <v>-17.49165407941707</v>
+        <v>-14.53299822887568</v>
       </c>
       <c r="F82">
-        <v>1.419588809910658</v>
+        <v>0.7799814871870759</v>
       </c>
       <c r="G82">
-        <v>-4.938126746139111</v>
+        <v>-3.996008386027778</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.235699732465098</v>
       </c>
       <c r="E83">
-        <v>-16.24540897555817</v>
+        <v>-17.09524957868164</v>
       </c>
       <c r="F83">
-        <v>0.8305599440672081</v>
+        <v>0.4905275507290531</v>
       </c>
       <c r="G83">
-        <v>-4.446749092836167</v>
+        <v>-3.000024139446962</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.718054953617894</v>
       </c>
       <c r="E84">
-        <v>-17.26018565898901</v>
+        <v>-18.76887847396244</v>
       </c>
       <c r="F84">
-        <v>0.6851516436493942</v>
+        <v>0.3688171849705273</v>
       </c>
       <c r="G84">
-        <v>-4.069793825007054</v>
+        <v>-4.084456231200486</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.133153656672361</v>
       </c>
       <c r="E85">
-        <v>-18.6673636721325</v>
+        <v>-18.4200546496256</v>
       </c>
       <c r="F85">
-        <v>0.7737438806439957</v>
+        <v>0.1166812000086222</v>
       </c>
       <c r="G85">
-        <v>-4.470280450529307</v>
+        <v>-3.120379022527166</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.481826997354214</v>
       </c>
       <c r="E86">
-        <v>-18.78500889837776</v>
+        <v>-19.03259415779912</v>
       </c>
       <c r="F86">
-        <v>0.2699068036066551</v>
+        <v>-0.04842402051295845</v>
       </c>
       <c r="G86">
-        <v>-4.384868375616111</v>
+        <v>-3.145552410807784</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.766210305843019</v>
       </c>
       <c r="E87">
-        <v>-22.00821820044726</v>
+        <v>-20.9399375966158</v>
       </c>
       <c r="F87">
-        <v>0.347309453724241</v>
+        <v>-0.08022173163682027</v>
       </c>
       <c r="G87">
-        <v>-3.035549603628881</v>
+        <v>-3.201229165687247</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.984052752519402</v>
       </c>
       <c r="E88">
-        <v>-21.39283481059692</v>
+        <v>-22.61019730723489</v>
       </c>
       <c r="F88">
-        <v>0.1292872951444251</v>
+        <v>-0.1463859212006252</v>
       </c>
       <c r="G88">
-        <v>-3.228081000556276</v>
+        <v>-2.96246931084947</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.134902176691803</v>
       </c>
       <c r="E89">
-        <v>-23.1848244310162</v>
+        <v>-23.82838398614226</v>
       </c>
       <c r="F89">
-        <v>-0.1027326158078968</v>
+        <v>-0.3926868861772106</v>
       </c>
       <c r="G89">
-        <v>-2.804900585362319</v>
+        <v>-3.151594156416954</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.215470836272501</v>
       </c>
       <c r="E90">
-        <v>-24.98179990131793</v>
+        <v>-24.8077389458851</v>
       </c>
       <c r="F90">
-        <v>0.008568485167050334</v>
+        <v>-0.627894354895505</v>
       </c>
       <c r="G90">
-        <v>-3.696718516549966</v>
+        <v>-2.474494898360897</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.221514866546061</v>
       </c>
       <c r="E91">
-        <v>-27.09004456101088</v>
+        <v>-25.92804718759069</v>
       </c>
       <c r="F91">
-        <v>-0.3465211424517913</v>
+        <v>-0.3812868939798838</v>
       </c>
       <c r="G91">
-        <v>-4.033659220445909</v>
+        <v>-3.438231120843672</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.149110874577405</v>
       </c>
       <c r="E92">
-        <v>-28.28800254652599</v>
+        <v>-27.29464101667743</v>
       </c>
       <c r="F92">
-        <v>-0.8911321197897291</v>
+        <v>-1.385489360269432</v>
       </c>
       <c r="G92">
-        <v>-4.021195016490553</v>
+        <v>-3.358039776245906</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.995080166928899</v>
       </c>
       <c r="E93">
-        <v>-29.62876143139898</v>
+        <v>-28.73515765546539</v>
       </c>
       <c r="F93">
-        <v>-0.9937660126291851</v>
+        <v>-1.253488186265928</v>
       </c>
       <c r="G93">
-        <v>-3.602010429762496</v>
+        <v>-3.357188966042313</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.75962785069005</v>
       </c>
       <c r="E94">
-        <v>-32.07440683974443</v>
+        <v>-31.70768195765527</v>
       </c>
       <c r="F94">
-        <v>-0.9605269422244521</v>
+        <v>-1.231736915003219</v>
       </c>
       <c r="G94">
-        <v>-3.529459824269368</v>
+        <v>-3.519971800753816</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.445696433705439</v>
       </c>
       <c r="E95">
-        <v>-34.22358664022972</v>
+        <v>-33.15952657417341</v>
       </c>
       <c r="F95">
-        <v>-0.6233292221386769</v>
+        <v>-1.373950202348435</v>
       </c>
       <c r="G95">
-        <v>-3.351988099000118</v>
+        <v>-3.960333947296591</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.058878355016402</v>
       </c>
       <c r="E96">
-        <v>-35.28143363994751</v>
+        <v>-36.29491517981215</v>
       </c>
       <c r="F96">
-        <v>-1.173030517166818</v>
+        <v>-1.704313891361114</v>
       </c>
       <c r="G96">
-        <v>-3.85077475321995</v>
+        <v>-3.669982550774812</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.614432757291605</v>
       </c>
       <c r="E97">
-        <v>-38.84811411007678</v>
+        <v>-37.70747754855076</v>
       </c>
       <c r="F97">
-        <v>-1.553956924078976</v>
+        <v>-1.624244726573917</v>
       </c>
       <c r="G97">
-        <v>-4.033900890270275</v>
+        <v>-4.099486107948777</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.118842075406113</v>
       </c>
       <c r="E98">
-        <v>-40.23681142079496</v>
+        <v>-40.30085762868544</v>
       </c>
       <c r="F98">
-        <v>-1.438936453465459</v>
+        <v>-1.753369808954901</v>
       </c>
       <c r="G98">
-        <v>-4.03928383731713</v>
+        <v>-4.343877200748854</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.6057084156271573</v>
       </c>
       <c r="E99">
-        <v>-42.90828050671791</v>
+        <v>-41.44635324282169</v>
       </c>
       <c r="F99">
-        <v>-1.862233853030812</v>
+        <v>-2.086647694490629</v>
       </c>
       <c r="G99">
-        <v>-3.540192612907685</v>
+        <v>-4.725218941417502</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.07547924713284457</v>
       </c>
       <c r="E100">
-        <v>-44.29853334825773</v>
+        <v>-44.4127527839162</v>
       </c>
       <c r="F100">
-        <v>-1.675919113527953</v>
+        <v>-2.24974992263224</v>
       </c>
       <c r="G100">
-        <v>-5.095804719629059</v>
+        <v>-5.39250574249516</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.4142531609200898</v>
       </c>
       <c r="E101">
-        <v>-47.47604808335282</v>
+        <v>-46.15518957750655</v>
       </c>
       <c r="F101">
-        <v>-1.628983816485333</v>
+        <v>-1.995918269596805</v>
       </c>
       <c r="G101">
-        <v>-4.906401788236275</v>
+        <v>-5.409833137847706</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.8927902902892695</v>
       </c>
       <c r="E102">
-        <v>-48.51803410285875</v>
+        <v>-48.2140738705159</v>
       </c>
       <c r="F102">
-        <v>-2.313462144683759</v>
+        <v>-2.387567892538202</v>
       </c>
       <c r="G102">
-        <v>-4.395442258068543</v>
+        <v>-5.162303647876398</v>
       </c>
     </row>
   </sheetData>
